--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -416,22 +416,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="33" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -510,17 +510,17 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>e2_report_mobility_ind_t</t>
+          <t>band_parameters_t</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>UInt32</t>
+          <t>rrc_bitmask_t</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>ho_attempt</t>
+          <t>bitmask</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>UI32</t>
+          <t>UI16</t>
         </is>
       </c>
       <c r="F2" s="1" t="b">
@@ -540,45 +540,29 @@
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>BITMASK</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr"/>
+      <c r="K2" s="1" t="inlineStr"/>
+      <c r="L2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr"/>
       <c r="N2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>e2_report_mobility_ind_t</t>
+          <t>band_parameters_t</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>UInt32</t>
+          <t>UInt8</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>ho_succ</t>
+          <t>band_id</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -588,7 +572,7 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>UI32</t>
+          <t>UI8</t>
         </is>
       </c>
       <c r="F3" s="1" t="b">
@@ -608,7 +592,7 @@
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>H</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
@@ -618,7 +602,7 @@
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr"/>
@@ -626,17 +610,17 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>e2_report_mobility_ind_t</t>
+          <t>band_parameters_t</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>UInt32</t>
+          <t>UInt16</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>ho_failure</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -646,7 +630,7 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>UI32</t>
+          <t>UI16</t>
         </is>
       </c>
       <c r="F4" s="1" t="b">
@@ -666,7 +650,7 @@
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr">
@@ -676,7 +660,7 @@
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="N4" s="1" t="inlineStr"/>
@@ -684,17 +668,17 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>e2sm_rrc_ric_indication_t</t>
+          <t>band_parameters_t</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>UInt16</t>
+          <t>UInt8</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>bitmask</t>
+          <t>optional_param_id</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -704,7 +688,7 @@
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>UI16</t>
+          <t>UI8</t>
         </is>
       </c>
       <c r="F5" s="1" t="b">
@@ -714,29 +698,45 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>BITMASK</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr"/>
-      <c r="L5" s="1" t="inlineStr"/>
-      <c r="M5" s="1" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>BAND_PARAM_BITMASK_OPTIONAL_PARAM_ID_PRESENT</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>e2sm_rrc_ric_indication_t</t>
+          <t>band_parameters_t</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>UInt32</t>
+          <t>UInt8</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>ric_request_id</t>
+          <t>optional_param_data</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>UI32</t>
+          <t>UI8</t>
         </is>
       </c>
       <c r="F6" s="1" t="b">
@@ -756,17 +756,17 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>BAND_PARAM_BITMASK_OPTIONAL_PARAM_DATA_PRESENT</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255</t>
         </is>
       </c>
       <c r="N6" s="1" t="inlineStr"/>
@@ -784,25 +784,29 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>e2sm_rrc_ric_indication_t</t>
+          <t>device_config_t</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>e2_report_mobility_ind_t</t>
+          <t>UInt16</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>report_mobility_ind</t>
+          <t>bitmask</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>STRUCT</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n"/>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>UI16</t>
+        </is>
+      </c>
       <c r="F7" s="1" t="b">
         <v>0</v>
       </c>
@@ -810,30 +814,976 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr">
         <is>
+          <t>BITMASK</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
+      <c r="L7" s="1" t="inlineStr"/>
+      <c r="M7" s="1" t="inlineStr"/>
+      <c r="N7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>device_config_t</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>UInt8</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>UI8</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="n"/>
+      <c r="H8" s="1" t="inlineStr"/>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>device_config_t</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>rf_parameters_t</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>rf_params</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>STRUCT</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="n"/>
+      <c r="F9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="n"/>
+      <c r="H9" s="1" t="inlineStr"/>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" s="1" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>device_config_t</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>UInt8</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>extra_data_config</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>UI8</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="n"/>
+      <c r="H10" s="1" t="inlineStr"/>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>IND_RIC_MOBILITY_REPORT_PRESENT</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>CONFIG_PRESENT</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N7" s="1" t="inlineStr"/>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>device_config_t</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>octet_string_t</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>extra_data</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>STRUCT</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr"/>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>DEVICE_CONFIG_BITMASK_EXTRA_DATA_PRESENT</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>OCTET_STRING</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr"/>
+      <c r="M11" s="1" t="inlineStr"/>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>device_config_t</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>UInt16</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>band_count</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>UI16</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="inlineStr"/>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="inlineStr">
+        <is>
+          <t>MAX_COUNT</t>
+        </is>
+      </c>
+      <c r="N12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>device_config_t</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>band_parameters_t</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>band_data</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>STRUCT</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="n"/>
+      <c r="F13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>band_count</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>OCTET_STRING</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr"/>
+      <c r="M13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>device_config_t</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>UInt8</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>list_id</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>UI8</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>OCTET_STRING</t>
+        </is>
+      </c>
+      <c r="L14" s="1" t="inlineStr"/>
+      <c r="M14" s="1" t="inlineStr"/>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>device_config_t</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>plmn_id_t</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>plmn</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>STRUCT</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="n"/>
+      <c r="F15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="n"/>
+      <c r="H15" s="1" t="inlineStr"/>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>octet_string_t</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>UInt8</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>length_a</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>UI8</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="n"/>
+      <c r="H16" s="1" t="inlineStr"/>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>MAX_OCTET_STRING_LEN</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>octet_string_t</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>UInt16</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>data_a</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>UI16</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>MAX_OCTET_STRING_LEN</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>length_a</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>OCTET_STRING</t>
+        </is>
+      </c>
+      <c r="L17" s="1" t="inlineStr"/>
+      <c r="M17" s="1" t="inlineStr"/>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>plmn_id_t</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>UInt8</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>plmn_count</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>UI8</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1" t="n"/>
+      <c r="H18" s="1" t="inlineStr"/>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>MAX_OCTET_STRING_LEN</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>plmn_id_t</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>UInt8</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>UI8</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>MAX_OCTET_STRING_LEN</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>plmn_count</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr">
+        <is>
+          <t>OCTET_STRING</t>
+        </is>
+      </c>
+      <c r="L19" s="1" t="inlineStr"/>
+      <c r="M19" s="1" t="inlineStr"/>
+      <c r="N19" s="1" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>rf_parameters_t</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>rrc_bitmask_t</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>bitmask</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>UI16</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="n"/>
+      <c r="H20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>BITMASK</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
+      <c r="L20" s="1" t="inlineStr"/>
+      <c r="M20" s="1" t="inlineStr"/>
+      <c r="N20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>rf_parameters_t</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>UInt16</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>UI16</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1" t="n"/>
+      <c r="H21" s="1" t="inlineStr"/>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M21" s="1" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="N21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>rf_parameters_t</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>UInt8</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>num_bands</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>UI8</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1" t="n"/>
+      <c r="H22" s="1" t="inlineStr"/>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L22" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="1" t="inlineStr">
+        <is>
+          <t>MAX_BANDS</t>
+        </is>
+      </c>
+      <c r="N22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>rf_parameters_t</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>band_parameters_t</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>bands</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>STRUCT</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="n"/>
+      <c r="F23" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>MAX_BANDS</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>num_bands</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr">
+        <is>
+          <t>OCTET_STRING</t>
+        </is>
+      </c>
+      <c r="L23" s="1" t="inlineStr"/>
+      <c r="M23" s="1" t="inlineStr"/>
+      <c r="N23" s="1" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>rf_parameters_t</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>octet_string_t</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>config_blob</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>STRUCT</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="n"/>
+      <c r="F24" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr"/>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t>RF_PARAM_BITMASK_CONFIG_BLOB_PRESENT</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="inlineStr">
+        <is>
+          <t>OCTET_STRING</t>
+        </is>
+      </c>
+      <c r="L24" s="1" t="inlineStr"/>
+      <c r="M24" s="1" t="inlineStr"/>
+      <c r="N24" s="1" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -419,19 +419,19 @@
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="33" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -510,17 +510,17 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>band_parameters_t</t>
+          <t>e2_report_mobility_req_t</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>rrc_bitmask_t</t>
+          <t>UInt8</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>bitmask</t>
+          <t>is_ho_attempt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>UI16</t>
+          <t>UI8</t>
         </is>
       </c>
       <c r="F2" s="1" t="b">
@@ -540,19 +540,35 @@
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>BITMASK</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr"/>
-      <c r="K2" s="1" t="inlineStr"/>
-      <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>band_parameters_t</t>
+          <t>e2_report_mobility_req_t</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -562,7 +578,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>band_id</t>
+          <t>is_ho_succ</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -592,7 +608,7 @@
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
@@ -602,7 +618,7 @@
       </c>
       <c r="M3" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N3" s="1" t="inlineStr"/>
@@ -610,17 +626,17 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>band_parameters_t</t>
+          <t>e2_report_mobility_req_t</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>UInt16</t>
+          <t>UInt8</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>is_ho_failure</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -630,7 +646,7 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>UI16</t>
+          <t>UI8</t>
         </is>
       </c>
       <c r="F4" s="1" t="b">
@@ -660,7 +676,7 @@
       </c>
       <c r="M4" s="1" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N4" s="1" t="inlineStr"/>
@@ -668,17 +684,17 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>band_parameters_t</t>
+          <t>e2ap_ric_action_list_t</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>UInt8</t>
+          <t>UInt16</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>optional_param_id</t>
+          <t>bitmask</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -688,7 +704,7 @@
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>UI8</t>
+          <t>UI16</t>
         </is>
       </c>
       <c r="F5" s="1" t="b">
@@ -698,45 +714,29 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>BAND_PARAM_BITMASK_OPTIONAL_PARAM_ID_PRESENT</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="L5" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="1" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>BITMASK</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
+      <c r="L5" s="1" t="inlineStr"/>
+      <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>band_parameters_t</t>
+          <t>e2ap_ric_action_list_t</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>UInt8</t>
+          <t>UInt32</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>optional_param_data</t>
+          <t>report_period_ms</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>UI8</t>
+          <t>UI32</t>
         </is>
       </c>
       <c r="F6" s="1" t="b">
@@ -756,17 +756,17 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>BAND_PARAM_BITMASK_OPTIONAL_PARAM_DATA_PRESENT</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="M6" s="1" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N6" s="1" t="inlineStr"/>
@@ -784,17 +784,17 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>device_config_t</t>
+          <t>e2ap_ric_action_list_t</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>UInt16</t>
+          <t>UInt32</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>bitmask</t>
+          <t>action_id</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>UI16</t>
+          <t>UI32</t>
         </is>
       </c>
       <c r="F7" s="1" t="b">
@@ -814,19 +814,35 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>BITMASK</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr"/>
-      <c r="L7" s="1" t="inlineStr"/>
-      <c r="M7" s="1" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N7" s="1" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>device_config_t</t>
+          <t>e2ap_ric_action_list_t</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
@@ -836,7 +852,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>action_type</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -866,7 +882,7 @@
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
@@ -876,7 +892,7 @@
       </c>
       <c r="M8" s="1" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N8" s="1" t="inlineStr"/>
@@ -884,17 +900,17 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>device_config_t</t>
+          <t>e2ap_ric_action_list_t</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>rf_parameters_t</t>
+          <t>rrc_ncgi_t</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>rf_params</t>
+          <t>nr_cgi</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -938,29 +954,25 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>device_config_t</t>
+          <t>e2ap_ric_action_list_t</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>UInt8</t>
+          <t>e2_report_mobility_req_t</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>extra_data_config</t>
+          <t>report_mobility_req</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>PRIMITIVE</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>UI8</t>
-        </is>
-      </c>
+          <t>STRUCT</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="n"/>
       <c r="F10" s="1" t="b">
         <v>0</v>
       </c>
@@ -973,7 +985,7 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>CONFIG_PRESENT</t>
+          <t>E2AP_REPORT_MOBILITY</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
@@ -996,61 +1008,65 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>device_config_t</t>
+          <t>rrc_e2sm_kpm_ric_sub_req_t</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>octet_string_t</t>
+          <t>UInt32</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>extra_data</t>
+          <t>ric_request_id</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>STRUCT</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="n"/>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>UI32</t>
+        </is>
+      </c>
       <c r="F11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="n"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>DEVICE_CONFIG_BITMASK_EXTRA_DATA_PRESENT</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>OCTET_STRING</t>
-        </is>
-      </c>
-      <c r="L11" s="1" t="inlineStr"/>
-      <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>device_config_t</t>
+          <t>rrc_e2sm_kpm_ric_sub_req_t</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
@@ -1060,7 +1076,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>band_count</t>
+          <t>ran_function_id</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
@@ -1090,7 +1106,7 @@
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr">
@@ -1100,7 +1116,7 @@
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
-          <t>MAX_COUNT</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr"/>
@@ -1108,38 +1124,34 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>device_config_t</t>
+          <t>rrc_e2sm_kpm_ric_sub_req_t</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>band_parameters_t</t>
+          <t>UInt8</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>band_data</t>
+          <t>num_action</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>STRUCT</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="n"/>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>UI8</t>
+        </is>
+      </c>
       <c r="F13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="inlineStr">
-        <is>
-          <t>band_count</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="n"/>
+      <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr">
         <is>
           <t>M</t>
@@ -1152,21 +1164,25 @@
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>OCTET_STRING</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="inlineStr"/>
-      <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>VARIABLE</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>device_config_t</t>
+          <t>rrc_e2sm_kpm_ric_sub_req_t</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
@@ -1176,7 +1192,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>list_id</t>
+          <t>periodic</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -1190,13 +1206,9 @@
         </is>
       </c>
       <c r="F14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="n"/>
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr">
         <is>
@@ -1210,31 +1222,35 @@
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>OCTET_STRING</t>
-        </is>
-      </c>
-      <c r="L14" s="1" t="inlineStr"/>
-      <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="1" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="1" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>device_config_t</t>
+          <t>rrc_e2sm_kpm_ric_sub_req_t</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>plmn_id_t</t>
+          <t>e2ap_ric_action_list_t</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>plmn</t>
+          <t>action_list</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -1244,10 +1260,18 @@
       </c>
       <c r="E15" s="1" t="n"/>
       <c r="F15" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1" t="n"/>
-      <c r="H15" s="1" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>ACTION_MAX</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>num_action</t>
+        </is>
+      </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
           <t>M</t>
@@ -1260,25 +1284,21 @@
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L15" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N15" s="1" t="inlineStr"/>
+          <t>OCTET_STRING</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="inlineStr"/>
+      <c r="M15" s="1" t="inlineStr"/>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>octet_string_t</t>
+          <t>rrc_mnc_t</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
@@ -1288,7 +1308,7 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>length_a</t>
+          <t>count</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -1323,12 +1343,12 @@
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
-          <t>MAX_OCTET_STRING_LEN</t>
+          <t>MAX_MNC_OCTET_SIZE</t>
         </is>
       </c>
       <c r="N16" s="1" t="inlineStr"/>
@@ -1336,17 +1356,17 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>octet_string_t</t>
+          <t>rrc_mnc_t</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>UInt16</t>
+          <t>UInt8</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>data_a</t>
+          <t>mnc</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -1356,7 +1376,7 @@
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>UI16</t>
+          <t>UI8</t>
         </is>
       </c>
       <c r="F17" s="1" t="b">
@@ -1364,12 +1384,12 @@
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>MAX_OCTET_STRING_LEN</t>
+          <t>MAX_MNC_OCTET_SIZE</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>length_a</t>
+          <t>count</t>
         </is>
       </c>
       <c r="I17" s="1" t="inlineStr">
@@ -1398,29 +1418,25 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>plmn_id_t</t>
+          <t>rrc_ncgi_t</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>UInt8</t>
+          <t>rrc_plmn_identity_t</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>plmn_count</t>
+          <t>plmn_identity</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>PRIMITIVE</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>UI8</t>
-        </is>
-      </c>
+          <t>STRUCT</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="n"/>
       <c r="F18" s="1" t="b">
         <v>0</v>
       </c>
@@ -1438,7 +1454,7 @@
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
@@ -1448,7 +1464,7 @@
       </c>
       <c r="M18" s="1" t="inlineStr">
         <is>
-          <t>MAX_OCTET_STRING_LEN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N18" s="1" t="inlineStr"/>
@@ -1456,42 +1472,30 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>plmn_id_t</t>
+          <t>rrc_ncgi_t</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>UInt8</t>
+          <t>rrc_nr_cell_identity_t</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>nr_cell_identity</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>PRIMITIVE</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
-        <is>
-          <t>UI8</t>
-        </is>
-      </c>
+          <t>STRUCT</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n"/>
       <c r="F19" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>MAX_OCTET_STRING_LEN</t>
-        </is>
-      </c>
-      <c r="H19" s="1" t="inlineStr">
-        <is>
-          <t>plmn_count</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="n"/>
+      <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr">
         <is>
           <t>M</t>
@@ -1504,31 +1508,35 @@
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>OCTET_STRING</t>
-        </is>
-      </c>
-      <c r="L19" s="1" t="inlineStr"/>
-      <c r="M19" s="1" t="inlineStr"/>
-      <c r="N19" s="1" t="inlineStr">
-        <is>
-          <t>VARIABLE</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="1" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>rf_parameters_t</t>
+          <t>rrc_nr_cell_identity_t</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>rrc_bitmask_t</t>
+          <t>UInt32</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>bitmask</t>
+          <t>numbits</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
@@ -1538,7 +1546,7 @@
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>UI16</t>
+          <t>UI32</t>
         </is>
       </c>
       <c r="F20" s="1" t="b">
@@ -1548,29 +1556,45 @@
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>BITMASK</t>
-        </is>
-      </c>
-      <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr"/>
-      <c r="L20" s="1" t="inlineStr"/>
-      <c r="M20" s="1" t="inlineStr"/>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N20" s="1" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>rf_parameters_t</t>
+          <t>rrc_nr_cell_identity_t</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>UInt16</t>
+          <t>UInt8</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
@@ -1580,14 +1604,22 @@
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>UI16</t>
+          <t>UI8</t>
         </is>
       </c>
       <c r="F21" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1" t="n"/>
-      <c r="H21" s="1" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>numbits</t>
+        </is>
+      </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
           <t>M</t>
@@ -1600,35 +1632,31 @@
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="1" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="N21" s="1" t="inlineStr"/>
+          <t>OCTET_STRING</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="inlineStr"/>
+      <c r="M21" s="1" t="inlineStr"/>
+      <c r="N21" s="1" t="inlineStr">
+        <is>
+          <t>VARIABLE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>rf_parameters_t</t>
+          <t>rrc_plmn_identity_t</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>UInt8</t>
+          <t>UInt16</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>num_bands</t>
+          <t>presence_bitmask</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
@@ -1638,7 +1666,7 @@
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>UI8</t>
+          <t>UI16</t>
         </is>
       </c>
       <c r="F22" s="1" t="b">
@@ -1648,74 +1676,58 @@
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="L22" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="1" t="inlineStr">
-        <is>
-          <t>MAX_BANDS</t>
-        </is>
-      </c>
+          <t>BITMASK</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
+      <c r="L22" s="1" t="inlineStr"/>
+      <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>rf_parameters_t</t>
+          <t>rrc_plmn_identity_t</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>band_parameters_t</t>
+          <t>UInt8</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>bands</t>
+          <t>mcc</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>STRUCT</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="n"/>
+          <t>PRIMITIVE</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>UI8</t>
+        </is>
+      </c>
       <c r="F23" s="1" t="b">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>MAX_BANDS</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>num_bands</t>
-        </is>
-      </c>
+          <t>MCC_OCTET_SIZE</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>PLMN_IDENTITY_MCC_PRESENCE_FLAG</t>
         </is>
       </c>
       <c r="K23" s="1" t="inlineStr">
@@ -1727,24 +1739,24 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>VARIABLE</t>
+          <t>FIXED</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>rf_parameters_t</t>
+          <t>rrc_plmn_identity_t</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>octet_string_t</t>
+          <t>rrc_mnc_t</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>config_blob</t>
+          <t>mnc</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -1754,36 +1766,36 @@
       </c>
       <c r="E24" s="1" t="n"/>
       <c r="F24" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G24" s="1" t="n"/>
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>M</t>
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>RF_PARAM_BITMASK_CONFIG_BLOB_PRESENT</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>OCTET_STRING</t>
-        </is>
-      </c>
-      <c r="L24" s="1" t="inlineStr"/>
-      <c r="M24" s="1" t="inlineStr"/>
-      <c r="N24" s="1" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L24" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N24" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
